--- a/SOS_benzene3.xlsx
+++ b/SOS_benzene3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.397</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="12">
@@ -530,10 +530,10 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.2098</v>
+        <v>-1.391</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6985</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="13">
@@ -541,10 +541,10 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.2098</v>
+        <v>-1.735</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.6985</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="14">
@@ -552,10 +552,10 @@
         <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.397</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="15">
@@ -563,10 +563,10 @@
         <v>4</v>
       </c>
       <c r="B15" t="n">
-        <v>1.2098</v>
+        <v>0.77</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.6985</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="16">
@@ -574,163 +574,174 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>1.2098</v>
+        <v>1.735</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6985</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ALPHA</t>
-        </is>
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Program units</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Atomic units</t>
+          <t>ALPHA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>alphaxx</t>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Program units</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atomic units</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>alphaxy</t>
+          <t>alphaxx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>alphaxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>alphayy</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BETA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Program units</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Atomic units</t>
+          <t>BETA</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>betaxxx</t>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Program units</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Atomic units</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>betaxxy</t>
+          <t>betaxxx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>betaxyy</t>
+          <t>betaxxy</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>betaxyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>betayyy</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>GAMMA</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Program units</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Atomic units</t>
+          <t>GAMMA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gammaxxxx</t>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Program units</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Atomic units</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gammaxxxy</t>
+          <t>gammaxxxx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gammaxxyy</t>
+          <t>gammaxxxy</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gammaxyyy</t>
+          <t>gammaxxyy</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t>gammaxyyy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>gammayyyy</t>
         </is>
